--- a/starter_pack_el_salvador/data/entity_files_uncalibrated/El_Salvador_Entity_Drought_Beans.xlsx
+++ b/starter_pack_el_salvador/data/entity_files_uncalibrated/El_Salvador_Entity_Drought_Beans.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19EB89B7-1582-4B54-95E3-FA03B27D1EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{841E5DCA-CCB9-46F5-AC0E-3563D4E59958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10908" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,7 +78,7 @@
     <t>Value_unit</t>
   </si>
   <si>
-    <t>USD</t>
+    <t>kg</t>
   </si>
   <si>
     <t>impact_fun_id</t>
